--- a/src/main/resources/templates/Bulletin_carbonev3.xlsx
+++ b/src/main/resources/templates/Bulletin_carbonev3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shéridan and Asher\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shéridan and Asher\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB74AA03-D10C-4013-B688-89BA416FC98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C5D10E6-C220-436C-996A-D4A1905B718E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="84">
   <si>
     <t>BULLETIN DE PAIE - {d.periodePaie.affiche}</t>
   </si>
@@ -278,9 +278,6 @@
   <si>
     <t>***Dans votre intérêt et pour vous aider à faire valoir vos droits, conservez ce bulletin sans limitation de durée.***</t>
   </si>
-  <si>
-    <t>{d.bulletinPaie[i+1].jourTravail}</t>
-  </si>
 </sst>
 </file>
 
@@ -390,7 +387,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="62">
+  <borders count="63">
     <border>
       <left/>
       <right/>
@@ -1071,11 +1068,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1366,7 +1374,6 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1375,6 +1382,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2129,7 +2145,7 @@
         <v>46</v>
       </c>
       <c r="F14" s="63"/>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="128" t="s">
         <v>47</v>
       </c>
       <c r="H14" s="18" t="s">
@@ -2161,16 +2177,17 @@
       <c r="Z14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="14.5">
-      <c r="B15" s="124" t="s">
+      <c r="B15" s="123" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="125"/>
-      <c r="D15" s="125"/>
-      <c r="F15" s="122" t="s">
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="126" t="s">
-        <v>84</v>
+      <c r="F15" s="126"/>
+      <c r="G15" s="125" t="s">
+        <v>47</v>
       </c>
       <c r="H15" s="18" t="s">
         <v>54</v>
@@ -2187,7 +2204,7 @@
       <c r="L15" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="M15" s="123"/>
+      <c r="M15" s="122"/>
     </row>
     <row r="16" spans="1:26" ht="9.75" customHeight="1">
       <c r="A16" s="23"/>
@@ -8932,7 +8949,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="57">
     <mergeCell ref="A26:K26"/>
     <mergeCell ref="G20:H21"/>
     <mergeCell ref="I20:I21"/>
@@ -8989,6 +9006,7 @@
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E17:I18"/>
     <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
   </mergeCells>
   <pageMargins left="0.44" right="0.1875" top="0.44" bottom="0.41" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="92" orientation="portrait" r:id="rId1"/>

--- a/src/main/resources/templates/Bulletin_carbonev3.xlsx
+++ b/src/main/resources/templates/Bulletin_carbonev3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10113"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shéridan and Asher\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbookpro2019/IdeaProjects/hrm_hyban/src/main/resources/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C5D10E6-C220-436C-996A-D4A1905B718E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46FC9F2B-A650-1149-A09C-1A1DBD86E73D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="35840" windowHeight="20720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mars_2023 (2)" sheetId="1" r:id="rId1"/>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t xml:space="preserve">Nombre de Part             </t>
-  </si>
-  <si>
-    <t>dd.bulletinPaie.nombrePart}</t>
   </si>
   <si>
     <t>N° de CNPS</t>
@@ -278,6 +275,9 @@
   <si>
     <t>***Dans votre intérêt et pour vous aider à faire valoir vos droits, conservez ce bulletin sans limitation de durée.***</t>
   </si>
+  <si>
+    <t>d.bulletinPaie.nombrePart}</t>
+  </si>
 </sst>
 </file>
 
@@ -313,15 +313,18 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -343,6 +346,7 @@
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1231,37 +1235,97 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="9" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="7" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1274,7 +1338,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1284,6 +1347,7 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1296,11 +1360,6 @@
     <xf numFmtId="3" fontId="9" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="9" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1309,87 +1368,32 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1413,11 +1417,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>25400</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="257175" cy="257175"/>
+    <xdr:ext cx="850900" cy="558800"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="image1.jpg">
@@ -1436,6 +1440,10 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="25400" y="0"/>
+          <a:ext cx="850900" cy="558800"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -1650,38 +1658,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" customWidth="1"/>
-    <col min="2" max="2" width="11.26953125" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="0.7265625" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" customWidth="1"/>
-    <col min="7" max="7" width="5.26953125" customWidth="1"/>
-    <col min="8" max="8" width="7.81640625" customWidth="1"/>
-    <col min="9" max="9" width="11.26953125" customWidth="1"/>
-    <col min="10" max="10" width="12.81640625" customWidth="1"/>
-    <col min="11" max="11" width="13.7265625" customWidth="1"/>
-    <col min="12" max="12" width="10.7265625" hidden="1" customWidth="1"/>
-    <col min="13" max="22" width="11.54296875" customWidth="1"/>
-    <col min="23" max="26" width="10.7265625" customWidth="1"/>
+    <col min="5" max="5" width="0.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" customWidth="1"/>
+    <col min="7" max="7" width="5.33203125" customWidth="1"/>
+    <col min="8" max="8" width="7.83203125" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" hidden="1" customWidth="1"/>
+    <col min="13" max="22" width="11.5" customWidth="1"/>
+    <col min="23" max="26" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="20.25" customHeight="1">
-      <c r="A1" s="74"/>
-      <c r="B1" s="76" t="s">
+      <c r="A1" s="100"/>
+      <c r="B1" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="78"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="71"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -1699,21 +1707,21 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="24" customHeight="1">
-      <c r="A2" s="75"/>
-      <c r="B2" s="79" t="s">
+      <c r="A2" s="101"/>
+      <c r="B2" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="80" t="s">
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="77"/>
-      <c r="K2" s="78"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="71"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1763,14 +1771,14 @@
       <c r="Z3" s="7"/>
     </row>
     <row r="4" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="82" t="s">
+      <c r="B4" s="107"/>
+      <c r="C4" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="83"/>
+      <c r="D4" s="109"/>
       <c r="E4" s="3"/>
       <c r="F4" s="8" t="s">
         <v>7</v>
@@ -1778,12 +1786,12 @@
       <c r="G4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="84" t="s">
+      <c r="H4" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="86"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="112"/>
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
@@ -1801,14 +1809,14 @@
       <c r="Z4" s="7"/>
     </row>
     <row r="5" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A5" s="95" t="s">
+      <c r="A5" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="97" t="s">
+      <c r="B5" s="69"/>
+      <c r="C5" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="98"/>
+      <c r="D5" s="88"/>
       <c r="E5" s="3"/>
       <c r="F5" s="10" t="s">
         <v>12</v>
@@ -1816,12 +1824,12 @@
       <c r="G5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="90" t="s">
+      <c r="H5" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="88"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="89"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="93"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
@@ -1839,27 +1847,27 @@
       <c r="Z5" s="7"/>
     </row>
     <row r="6" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A6" s="95" t="s">
+      <c r="A6" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="96"/>
-      <c r="C6" s="97" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="98"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="87" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="88"/>
       <c r="E6" s="3"/>
       <c r="F6" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="87" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="89"/>
+      <c r="H6" s="113" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="93"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
@@ -1877,27 +1885,27 @@
       <c r="Z6" s="7"/>
     </row>
     <row r="7" spans="1:26" ht="21" customHeight="1">
-      <c r="A7" s="95" t="s">
+      <c r="A7" s="86" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="69"/>
+      <c r="C7" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="96"/>
-      <c r="C7" s="97" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="98"/>
+      <c r="D7" s="88"/>
       <c r="E7" s="3"/>
       <c r="F7" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="88"/>
-      <c r="J7" s="88"/>
-      <c r="K7" s="89"/>
+      <c r="H7" s="91" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="93"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
@@ -1915,27 +1923,27 @@
       <c r="Z7" s="7"/>
     </row>
     <row r="8" spans="1:26" ht="20.25" customHeight="1">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="86" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="69"/>
+      <c r="C8" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="96"/>
-      <c r="C8" s="97" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="98"/>
+      <c r="D8" s="88"/>
       <c r="E8" s="3"/>
       <c r="F8" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="90" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="88"/>
-      <c r="J8" s="88"/>
-      <c r="K8" s="89"/>
+      <c r="H8" s="91" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="92"/>
+      <c r="J8" s="92"/>
+      <c r="K8" s="93"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
@@ -1953,27 +1961,27 @@
       <c r="Z8" s="7"/>
     </row>
     <row r="9" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A9" s="95" t="s">
+      <c r="A9" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="69"/>
+      <c r="C9" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="96"/>
-      <c r="C9" s="97" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="98"/>
+      <c r="D9" s="88"/>
       <c r="E9" s="3"/>
       <c r="F9" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H9" s="91" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="88"/>
-      <c r="J9" s="88"/>
-      <c r="K9" s="89"/>
+      <c r="H9" s="114" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="92"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="93"/>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
@@ -1991,27 +1999,27 @@
       <c r="Z9" s="7"/>
     </row>
     <row r="10" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A10" s="99" t="s">
+      <c r="A10" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="57"/>
+      <c r="C10" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="100"/>
-      <c r="C10" s="101" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="102"/>
+      <c r="D10" s="58"/>
       <c r="E10" s="3"/>
       <c r="F10" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="92" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="93"/>
-      <c r="J10" s="93"/>
-      <c r="K10" s="94"/>
+      <c r="H10" s="115" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="116"/>
+      <c r="J10" s="116"/>
+      <c r="K10" s="117"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
@@ -2029,19 +2037,19 @@
       <c r="Z10" s="7"/>
     </row>
     <row r="11" spans="1:26" ht="8.25" customHeight="1">
-      <c r="A11" s="103" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
+      <c r="A11" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
+      <c r="K11" s="69"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -2059,31 +2067,31 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="12" customHeight="1">
-      <c r="A12" s="104" t="s">
+      <c r="A12" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="106" t="s">
+      <c r="C12" s="79"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="60"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="106" t="s">
+      <c r="F12" s="80"/>
+      <c r="G12" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="61"/>
-      <c r="G12" s="107" t="s">
+      <c r="H12" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="108" t="s">
+      <c r="I12" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="109" t="s">
+      <c r="J12" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="110" t="s">
-        <v>41</v>
-      </c>
-      <c r="K12" s="111"/>
+      <c r="K12" s="66"/>
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
@@ -2101,20 +2109,20 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1">
-      <c r="A13" s="105"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="105"/>
+      <c r="A13" s="64"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
       <c r="J13" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" s="14" t="s">
         <v>42</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>43</v>
       </c>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
@@ -2134,31 +2142,31 @@
     </row>
     <row r="14" spans="1:26" ht="11.25" customHeight="1">
       <c r="A14" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="118" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="59" t="s">
+      <c r="C14" s="79"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="119" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="62" t="s">
+      <c r="F14" s="120"/>
+      <c r="G14" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="63"/>
-      <c r="G14" s="128" t="s">
+      <c r="H14" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="I14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="J14" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="J14" s="20" t="s">
+      <c r="K14" s="21" t="s">
         <v>50</v>
-      </c>
-      <c r="K14" s="21" t="s">
-        <v>51</v>
       </c>
       <c r="L14" s="22"/>
       <c r="M14" s="22"/>
@@ -2176,43 +2184,43 @@
       <c r="Y14" s="7"/>
       <c r="Z14" s="7"/>
     </row>
-    <row r="15" spans="1:26" ht="14.5">
-      <c r="B15" s="123" t="s">
+    <row r="15" spans="1:26">
+      <c r="B15" s="125" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="126"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="127" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="124"/>
-      <c r="D15" s="124"/>
-      <c r="E15" s="127" t="s">
+      <c r="F15" s="128"/>
+      <c r="G15" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="126"/>
-      <c r="G15" s="125" t="s">
-        <v>47</v>
-      </c>
-      <c r="H15" s="18" t="s">
+      <c r="I15" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="19" t="s">
+      <c r="J15" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="20" t="s">
+      <c r="K15" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="K15" s="21" t="s">
-        <v>57</v>
-      </c>
       <c r="L15" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="M15" s="122"/>
+        <v>43</v>
+      </c>
+      <c r="M15" s="53"/>
     </row>
     <row r="16" spans="1:26" ht="9.75" customHeight="1">
       <c r="A16" s="23"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="56"/>
+      <c r="B16" s="121"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="121"/>
+      <c r="F16" s="62"/>
       <c r="G16" s="24"/>
       <c r="H16" s="25"/>
       <c r="I16" s="26"/>
@@ -2239,17 +2247,17 @@
       <c r="B17" s="30"/>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
-      <c r="E17" s="65" t="s">
+      <c r="E17" s="122" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="123"/>
+      <c r="G17" s="123"/>
+      <c r="H17" s="123"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="94" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="70" t="s">
-        <v>59</v>
-      </c>
-      <c r="K17" s="67"/>
+      <c r="K17" s="95"/>
       <c r="L17" s="28"/>
       <c r="M17" s="28"/>
       <c r="N17" s="28"/>
@@ -2271,13 +2279,13 @@
       <c r="B18" s="32"/>
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="68"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="69"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="124"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="97"/>
       <c r="L18" s="33"/>
       <c r="M18" s="34"/>
       <c r="N18" s="7"/>
@@ -2296,7 +2304,7 @@
     </row>
     <row r="19" spans="1:26" ht="7.5" customHeight="1">
       <c r="A19" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -2325,30 +2333,30 @@
       <c r="Z19" s="7"/>
     </row>
     <row r="20" spans="1:26" ht="6" customHeight="1">
-      <c r="A20" s="72" t="s">
+      <c r="A20" s="98" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="C20" s="60"/>
+      <c r="D20" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="54"/>
-      <c r="D20" s="53" t="s">
+      <c r="E20" s="107"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="59" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="57"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="53" t="s">
+      <c r="H20" s="60"/>
+      <c r="I20" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="H20" s="54"/>
-      <c r="I20" s="118" t="s">
+      <c r="J20" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="J20" s="112" t="s">
+      <c r="K20" s="73" t="s">
         <v>65</v>
-      </c>
-      <c r="K20" s="113" t="s">
-        <v>66</v>
       </c>
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
@@ -2367,17 +2375,17 @@
       <c r="Z20" s="7"/>
     </row>
     <row r="21" spans="1:26" ht="6" customHeight="1">
-      <c r="A21" s="73"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="114"/>
+      <c r="A21" s="99"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="74"/>
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
       <c r="N21" s="7"/>
@@ -2396,25 +2404,25 @@
     </row>
     <row r="22" spans="1:26" ht="11.25" customHeight="1">
       <c r="A22" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="119" t="s">
+      <c r="C22" s="66"/>
+      <c r="D22" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="111"/>
-      <c r="D22" s="119" t="s">
+      <c r="E22" s="67"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="120"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="119" t="s">
-        <v>70</v>
-      </c>
-      <c r="H22" s="111"/>
+      <c r="H22" s="66"/>
       <c r="I22" s="37"/>
       <c r="J22" s="37"/>
       <c r="K22" s="38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
@@ -2434,13 +2442,13 @@
     </row>
     <row r="23" spans="1:26" ht="11.25" customHeight="1">
       <c r="A23" s="39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
-      <c r="E23" s="121"/>
-      <c r="F23" s="96"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="69"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
@@ -2466,33 +2474,33 @@
     </row>
     <row r="24" spans="1:26" ht="21.75" customHeight="1">
       <c r="A24" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="C24" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="115" t="s">
+      <c r="D24" s="71"/>
+      <c r="E24" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="78"/>
-      <c r="E24" s="115" t="s">
+      <c r="F24" s="71"/>
+      <c r="G24" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="F24" s="78"/>
-      <c r="G24" s="41" t="s">
+      <c r="H24" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="H24" s="43" t="s">
+      <c r="I24" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="I24" s="43" t="s">
+      <c r="J24" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="J24" s="41" t="s">
+      <c r="K24" s="41" t="s">
         <v>80</v>
-      </c>
-      <c r="K24" s="41" t="s">
-        <v>81</v>
       </c>
       <c r="L24" s="7"/>
       <c r="M24" s="7"/>
@@ -2512,13 +2520,13 @@
     </row>
     <row r="25" spans="1:26" ht="10.5" customHeight="1">
       <c r="A25" s="44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B25" s="45"/>
-      <c r="C25" s="116"/>
-      <c r="D25" s="78"/>
-      <c r="E25" s="116"/>
-      <c r="F25" s="78"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="71"/>
       <c r="G25" s="45">
         <v>30</v>
       </c>
@@ -2545,19 +2553,19 @@
       <c r="Z25" s="7"/>
     </row>
     <row r="26" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A26" s="117" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" s="100"/>
-      <c r="C26" s="100"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="100"/>
-      <c r="F26" s="100"/>
-      <c r="G26" s="100"/>
-      <c r="H26" s="100"/>
-      <c r="I26" s="100"/>
-      <c r="J26" s="100"/>
-      <c r="K26" s="102"/>
+      <c r="A26" s="56" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="58"/>
       <c r="L26" s="7"/>
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
@@ -8950,38 +8958,13 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="G20:H21"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:D13"/>
-    <mergeCell ref="E12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="I12:I13"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:I18"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E15:F15"/>
     <mergeCell ref="J17:K18"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="A1:A2"/>
@@ -8998,15 +8981,40 @@
     <mergeCell ref="H10:K10"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:D5"/>
+    <mergeCell ref="H5:K5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:D13"/>
+    <mergeCell ref="E12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="G20:H21"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B20:C21"/>
     <mergeCell ref="D20:F21"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:I18"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E15:F15"/>
   </mergeCells>
   <pageMargins left="0.44" right="0.1875" top="0.44" bottom="0.41" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="92" orientation="portrait" r:id="rId1"/>
